--- a/en/downloads/data-excel/11.2.1.xlsx
+++ b/en/downloads/data-excel/11.2.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="8070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -922,14 +922,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="36.42578125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
@@ -940,7 +940,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
@@ -951,7 +951,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -961,8 +961,9 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -990,8 +991,11 @@
       <c r="I4" s="5">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="18">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>27</v>
       </c>
@@ -1019,8 +1023,11 @@
       <c r="I5" s="16">
         <v>55.603276734707606</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J5" s="16">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>29</v>
       </c>
@@ -1035,8 +1042,9 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -1064,8 +1072,11 @@
       <c r="I7" s="8">
         <v>64.815870068283189</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J7" s="8">
+        <v>73.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -1093,8 +1104,11 @@
       <c r="I8" s="8">
         <v>49.843423517048826</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="8">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>37</v>
       </c>
@@ -1110,8 +1124,9 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
@@ -1139,8 +1154,11 @@
       <c r="I10" s="8">
         <v>55.846852199084964</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J10" s="8">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>41</v>
       </c>
@@ -1168,8 +1186,11 @@
       <c r="I11" s="8">
         <v>55.396573524258045</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J11" s="8">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
         <v>43</v>
       </c>
@@ -1185,8 +1206,9 @@
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>46</v>
       </c>
@@ -1214,8 +1236,11 @@
       <c r="I13" s="8">
         <v>56.841459998341435</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J13" s="8">
+        <v>63.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>49</v>
       </c>
@@ -1243,8 +1268,11 @@
       <c r="I14" s="8">
         <v>39.405155466620641</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J14" s="8">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>52</v>
       </c>
@@ -1272,8 +1300,11 @@
       <c r="I15" s="8">
         <v>71.515443042037774</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J15" s="8">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>55</v>
       </c>
@@ -1301,8 +1332,11 @@
       <c r="I16" s="8">
         <v>59.187474880557509</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J16" s="8">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>58</v>
       </c>
@@ -1330,8 +1364,11 @@
       <c r="I17" s="8">
         <v>44.681041326587682</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J17" s="8">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>61</v>
       </c>
@@ -1359,8 +1396,11 @@
       <c r="I18" s="8">
         <v>41.791860091300215</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J18" s="8">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>64</v>
       </c>
@@ -1388,8 +1428,11 @@
       <c r="I19" s="8">
         <v>63.928870055380102</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J19" s="8">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>67</v>
       </c>
@@ -1417,8 +1460,11 @@
       <c r="I20" s="8">
         <v>60.544747238121026</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J20" s="8">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>70</v>
       </c>
@@ -1446,8 +1492,11 @@
       <c r="I21" s="8">
         <v>97.912546195661392</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J21" s="8">
+        <v>98.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
         <v>101</v>
       </c>
@@ -1463,8 +1512,9 @@
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
-    </row>
-    <row r="23" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>103</v>
       </c>
@@ -1492,8 +1542,11 @@
       <c r="I23" s="8">
         <v>53.843789071495877</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J23" s="8">
+        <v>62.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>108</v>
       </c>
@@ -1521,8 +1574,11 @@
       <c r="I24" s="8">
         <v>56.474118627705991</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J24" s="8">
+        <v>63.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>109</v>
       </c>
@@ -1550,8 +1606,11 @@
       <c r="I25" s="8">
         <v>55.561580291086344</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J25" s="8">
+        <v>60.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
         <v>73</v>
       </c>
@@ -1567,8 +1626,9 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>75</v>
       </c>
@@ -1596,8 +1656,11 @@
       <c r="I27" s="8">
         <v>52.606025465127615</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J27" s="8">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>77</v>
       </c>
@@ -1625,8 +1688,11 @@
       <c r="I28" s="8">
         <v>57.236792190411222</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J28" s="8">
+        <v>63.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>79</v>
       </c>
@@ -1654,8 +1720,11 @@
       <c r="I29" s="8">
         <v>52.14412411595751</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J29" s="8">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>81</v>
       </c>
@@ -1683,8 +1752,11 @@
       <c r="I30" s="8">
         <v>58.899867561786387</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J30" s="8">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>84</v>
       </c>
@@ -1712,8 +1784,11 @@
       <c r="I31" s="8">
         <v>60.746138294784885</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J31" s="8">
+        <v>68.3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>86</v>
       </c>
@@ -1729,8 +1804,9 @@
       <c r="G32" s="33"/>
       <c r="H32" s="33"/>
       <c r="I32" s="33"/>
-    </row>
-    <row r="33" spans="1:9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J32" s="33"/>
+    </row>
+    <row r="33" spans="1:10" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="27" t="s">
         <v>88</v>
       </c>
@@ -1758,8 +1834,11 @@
       <c r="I33" s="33">
         <v>52.19516363306797</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J33" s="33">
+        <v>62.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="27" t="s">
         <v>90</v>
       </c>
@@ -1787,8 +1866,11 @@
       <c r="I34" s="33">
         <v>57.259390321892035</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J34" s="33">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
         <v>92</v>
       </c>
@@ -1816,8 +1898,11 @@
       <c r="I35" s="33">
         <v>52.31297951131355</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J35" s="33">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="27" t="s">
         <v>94</v>
       </c>
@@ -1845,8 +1930,11 @@
       <c r="I36" s="33">
         <v>56.454847922343262</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J36" s="33">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="29" t="s">
         <v>96</v>
       </c>
@@ -1874,8 +1962,11 @@
       <c r="I37" s="9">
         <v>58.590714884518619</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J37" s="9">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="34" t="s">
         <v>98</v>
       </c>
